--- a/docs/ValueSet-vs-tw-ltc-service-item.xlsx
+++ b/docs/ValueSet-vs-tw-ltc-service-item.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-vs-tw-ltc-service-item.xlsx
+++ b/docs/ValueSet-vs-tw-ltc-service-item.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-vs-tw-ltc-service-item.xlsx
+++ b/docs/ValueSet-vs-tw-ltc-service-item.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>長照 SDK－服務項目（計畫）</t>
+    <t>臺灣長照服務項目</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>此 ValueSet 用於表示長照 SDK 中的服務項目（計畫）。</t>
+    <t>此 ValueSet 涵蓋臺灣長照 2.0 給付之所有服務項目代碼，適用於長照服務之申請、核定與使用紀錄，包含照顧組合、專業服務、交通接送、喘息服務等項目。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-vs-tw-ltc-service-item.xlsx
+++ b/docs/ValueSet-vs-tw-ltc-service-item.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
